--- a/Simulacion/TPI/Informe/Tablas.xlsx
+++ b/Simulacion/TPI/Informe/Tablas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Desktop\Estudios_academicos\Sistemas-2025\Simulacion\TPI\Informe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Estudios\Sistemas-2025\Simulacion\TPI\Informe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BA3B56-24AD-4C18-80B4-8AA76C13D3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BC3FE1-1DA4-44CB-804C-9939B986F429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Calles</t>
   </si>
@@ -104,6 +93,15 @@
   </si>
   <si>
     <t>L =</t>
+  </si>
+  <si>
+    <t>Sumatoria lambda =</t>
+  </si>
+  <si>
+    <t>Autos por avenida (L) [cant. autos]</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -145,7 +143,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -310,11 +308,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -365,6 +376,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -647,16 +672,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:V34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="33.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="2"/>
+    <col min="3" max="3" width="33.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" style="2"/>
+    <col min="15" max="15" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.21875" customWidth="1"/>
+    <col min="17" max="17" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
@@ -671,8 +699,17 @@
       <c r="K2" s="16"/>
       <c r="L2" s="16"/>
       <c r="M2" s="17"/>
-    </row>
-    <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P2" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="18"/>
+    </row>
+    <row r="3" spans="3:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
@@ -697,8 +734,19 @@
       <c r="M3" s="12">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="4" spans="3:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="18"/>
+    </row>
+    <row r="4" spans="3:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
@@ -728,8 +776,20 @@
         <f>0.2*I4</f>
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P4" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="21">
+        <f>$K$33* (I4/$P$33)</f>
+        <v>10.05982905982906</v>
+      </c>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="19"/>
+      <c r="U4" s="19"/>
+      <c r="V4" s="18"/>
+    </row>
+    <row r="5" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C5" s="5" t="s">
         <v>4</v>
       </c>
@@ -760,8 +820,21 @@
         <f t="shared" ref="M5:M15" si="4">0.2*I5</f>
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P5" s="11">
+        <f>P4+1</f>
+        <v>2</v>
+      </c>
+      <c r="Q5" s="21">
+        <f t="shared" ref="Q5:Q15" si="5">$K$33* (I5/$P$33)</f>
+        <v>13.717948717948717</v>
+      </c>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
+      <c r="T5" s="19"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="18"/>
+    </row>
+    <row r="6" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C6" s="5" t="s">
         <v>9</v>
       </c>
@@ -770,7 +843,7 @@
         <v>4</v>
       </c>
       <c r="H6" s="11">
-        <f t="shared" ref="H6:H15" si="5">H5+1</f>
+        <f t="shared" ref="H6:H15" si="6">H5+1</f>
         <v>3</v>
       </c>
       <c r="I6" s="1">
@@ -792,8 +865,21 @@
         <f t="shared" si="4"/>
         <v>2.4000000000000004</v>
       </c>
-    </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P6" s="11">
+        <f t="shared" ref="P6:P15" si="7">P5+1</f>
+        <v>3</v>
+      </c>
+      <c r="Q6" s="21">
+        <f t="shared" si="5"/>
+        <v>10.974358974358974</v>
+      </c>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="18"/>
+    </row>
+    <row r="7" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
@@ -802,7 +888,7 @@
         <v>5</v>
       </c>
       <c r="H7" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="I7" s="1">
@@ -824,8 +910,21 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P7" s="11">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q7" s="21">
+        <f t="shared" si="5"/>
+        <v>4.5726495726495724</v>
+      </c>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="18"/>
+    </row>
+    <row r="8" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
@@ -834,7 +933,7 @@
         <v>6</v>
       </c>
       <c r="H8" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="I8" s="1">
@@ -856,8 +955,21 @@
         <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
-    </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P8" s="11">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="Q8" s="21">
+        <f t="shared" si="5"/>
+        <v>10.05982905982906</v>
+      </c>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="18"/>
+    </row>
+    <row r="9" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C9" s="5" t="s">
         <v>7</v>
       </c>
@@ -866,7 +978,7 @@
         <v>7</v>
       </c>
       <c r="H9" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="I9" s="1">
@@ -888,8 +1000,21 @@
         <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
-    </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P9" s="11">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="Q9" s="21">
+        <f t="shared" si="5"/>
+        <v>6.4017094017094021</v>
+      </c>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="18"/>
+    </row>
+    <row r="10" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
@@ -898,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="H10" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="I10" s="1">
@@ -920,8 +1045,21 @@
         <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
-    </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P10" s="11">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="Q10" s="21">
+        <f t="shared" si="5"/>
+        <v>7.3162393162393169</v>
+      </c>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="18"/>
+    </row>
+    <row r="11" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C11" s="5" t="s">
         <v>10</v>
       </c>
@@ -930,7 +1068,7 @@
         <v>9</v>
       </c>
       <c r="H11" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="I11" s="1">
@@ -952,8 +1090,21 @@
         <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
-    </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P11" s="11">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="Q11" s="21">
+        <f t="shared" si="5"/>
+        <v>8.2307692307692317</v>
+      </c>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="18"/>
+    </row>
+    <row r="12" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C12" s="5" t="s">
         <v>11</v>
       </c>
@@ -962,7 +1113,7 @@
         <v>10</v>
       </c>
       <c r="H12" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="I12" s="1">
@@ -984,8 +1135,21 @@
         <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="P12" s="11">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="Q12" s="21">
+        <f t="shared" si="5"/>
+        <v>5.4871794871794872</v>
+      </c>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="18"/>
+    </row>
+    <row r="13" spans="3:22" ht="15" x14ac:dyDescent="0.3">
       <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
@@ -994,7 +1158,7 @@
         <v>11</v>
       </c>
       <c r="H13" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
       <c r="I13" s="1">
@@ -1016,8 +1180,21 @@
         <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
-    </row>
-    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P13" s="11">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="Q13" s="21">
+        <f t="shared" si="5"/>
+        <v>11.888888888888888</v>
+      </c>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="18"/>
+    </row>
+    <row r="14" spans="3:22" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="8" t="s">
         <v>13</v>
       </c>
@@ -1026,7 +1203,7 @@
         <v>12</v>
       </c>
       <c r="H14" s="11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="I14" s="1">
@@ -1048,10 +1225,23 @@
         <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
       </c>
-    </row>
-    <row r="15" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P14" s="11">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="Q14" s="21">
+        <f t="shared" si="5"/>
+        <v>6.4017094017094021</v>
+      </c>
+      <c r="R14" s="19"/>
+      <c r="S14" s="19"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="19"/>
+      <c r="V14" s="18"/>
+    </row>
+    <row r="15" spans="3:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H15" s="13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
       <c r="I15" s="14">
@@ -1073,9 +1263,22 @@
         <f t="shared" si="4"/>
         <v>2.6</v>
       </c>
-    </row>
-    <row r="17" spans="8:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="8:13" x14ac:dyDescent="0.25">
+      <c r="P15" s="13">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="Q15" s="21">
+        <f t="shared" si="5"/>
+        <v>11.888888888888888</v>
+      </c>
+      <c r="R15" s="19"/>
+      <c r="S15" s="19"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="19"/>
+      <c r="V15" s="18"/>
+    </row>
+    <row r="17" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
       <c r="H18" s="15" t="s">
         <v>15</v>
       </c>
@@ -1085,7 +1288,7 @@
       <c r="L18" s="16"/>
       <c r="M18" s="17"/>
     </row>
-    <row r="19" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
       <c r="H19" s="11" t="s">
         <v>0</v>
       </c>
@@ -1105,12 +1308,12 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
       <c r="H20" s="11">
         <v>1</v>
       </c>
       <c r="I20" s="1">
-        <f>$K$33/I4</f>
+        <f>$K$33/$I4</f>
         <v>9.7272727272727266</v>
       </c>
       <c r="J20" s="1">
@@ -1130,296 +1333,308 @@
         <v>1.9454545454545453</v>
       </c>
     </row>
-    <row r="21" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="18"/>
       <c r="H21" s="11">
         <f>H20+1</f>
         <v>2</v>
       </c>
       <c r="I21" s="1">
-        <f>$K$33/I5</f>
+        <f t="shared" ref="I21:I31" si="8">$K$33/I5</f>
         <v>7.1333333333333337</v>
       </c>
       <c r="J21" s="1">
-        <f t="shared" ref="J21:J31" si="6">0.8*I21</f>
+        <f t="shared" ref="J21:J31" si="9">0.8*I21</f>
         <v>5.706666666666667</v>
       </c>
       <c r="K21" s="1">
-        <f t="shared" ref="K21:K31" si="7">0.6*I21</f>
+        <f t="shared" ref="K21:K31" si="10">0.6*I21</f>
         <v>4.28</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" ref="L21:L31" si="8">0.4*I21</f>
+        <f t="shared" ref="L21:L31" si="11">0.4*I21</f>
         <v>2.8533333333333335</v>
       </c>
       <c r="M21" s="6">
-        <f t="shared" ref="M21:M31" si="9">0.2*I21</f>
+        <f t="shared" ref="M21:M31" si="12">0.2*I21</f>
         <v>1.4266666666666667</v>
       </c>
     </row>
-    <row r="22" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C22" s="18"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="18"/>
       <c r="H22" s="11">
-        <f t="shared" ref="H22:H31" si="10">H21+1</f>
+        <f t="shared" ref="H22:H31" si="13">H21+1</f>
         <v>3</v>
       </c>
       <c r="I22" s="1">
-        <f>$K$33/I6</f>
+        <f t="shared" si="8"/>
         <v>8.9166666666666661</v>
       </c>
       <c r="J22" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>7.1333333333333329</v>
       </c>
       <c r="K22" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>5.35</v>
       </c>
       <c r="L22" s="1">
+        <f t="shared" si="11"/>
+        <v>3.5666666666666664</v>
+      </c>
+      <c r="M22" s="6">
+        <f t="shared" si="12"/>
+        <v>1.7833333333333332</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
+      <c r="H23" s="11">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="I23" s="1">
         <f t="shared" si="8"/>
+        <v>21.4</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="9"/>
+        <v>17.12</v>
+      </c>
+      <c r="K23" s="1">
+        <f t="shared" si="10"/>
+        <v>12.839999999999998</v>
+      </c>
+      <c r="L23" s="1">
+        <f t="shared" si="11"/>
+        <v>8.56</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="12"/>
+        <v>4.28</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="18"/>
+      <c r="H24" s="11">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="8"/>
+        <v>9.7272727272727266</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="9"/>
+        <v>7.7818181818181813</v>
+      </c>
+      <c r="K24" s="1">
+        <f t="shared" si="10"/>
+        <v>5.836363636363636</v>
+      </c>
+      <c r="L24" s="1">
+        <f t="shared" si="11"/>
+        <v>3.8909090909090907</v>
+      </c>
+      <c r="M24" s="6">
+        <f t="shared" si="12"/>
+        <v>1.9454545454545453</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H25" s="11">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="8"/>
+        <v>15.285714285714286</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="9"/>
+        <v>12.22857142857143</v>
+      </c>
+      <c r="K25" s="1">
+        <f t="shared" si="10"/>
+        <v>9.1714285714285708</v>
+      </c>
+      <c r="L25" s="1">
+        <f t="shared" si="11"/>
+        <v>6.1142857142857148</v>
+      </c>
+      <c r="M25" s="6">
+        <f t="shared" si="12"/>
+        <v>3.0571428571428574</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H26" s="11">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="8"/>
+        <v>13.375</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="9"/>
+        <v>10.700000000000001</v>
+      </c>
+      <c r="K26" s="1">
+        <f t="shared" si="10"/>
+        <v>8.0250000000000004</v>
+      </c>
+      <c r="L26" s="1">
+        <f t="shared" si="11"/>
+        <v>5.3500000000000005</v>
+      </c>
+      <c r="M26" s="6">
+        <f t="shared" si="12"/>
+        <v>2.6750000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H27" s="11">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="8"/>
+        <v>11.888888888888889</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="9"/>
+        <v>9.5111111111111111</v>
+      </c>
+      <c r="K27" s="1">
+        <f t="shared" si="10"/>
+        <v>7.1333333333333337</v>
+      </c>
+      <c r="L27" s="1">
+        <f t="shared" si="11"/>
+        <v>4.7555555555555555</v>
+      </c>
+      <c r="M27" s="6">
+        <f t="shared" si="12"/>
+        <v>2.3777777777777778</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H28" s="11">
+        <f t="shared" si="13"/>
+        <v>9</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="8"/>
+        <v>17.833333333333332</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="9"/>
+        <v>14.266666666666666</v>
+      </c>
+      <c r="K28" s="1">
+        <f t="shared" si="10"/>
+        <v>10.7</v>
+      </c>
+      <c r="L28" s="1">
+        <f t="shared" si="11"/>
+        <v>7.1333333333333329</v>
+      </c>
+      <c r="M28" s="6">
+        <f t="shared" si="12"/>
         <v>3.5666666666666664</v>
       </c>
-      <c r="M22" s="6">
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H29" s="11">
+        <f t="shared" si="13"/>
+        <v>10</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="8"/>
+        <v>8.2307692307692299</v>
+      </c>
+      <c r="J29" s="1">
         <f t="shared" si="9"/>
-        <v>1.7833333333333332</v>
-      </c>
-    </row>
-    <row r="23" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H23" s="11">
+        <v>6.5846153846153843</v>
+      </c>
+      <c r="K29" s="1">
         <f t="shared" si="10"/>
-        <v>4</v>
-      </c>
-      <c r="I23" s="1">
-        <f>$K$33/I7</f>
-        <v>21.4</v>
-      </c>
-      <c r="J23" s="1">
-        <f t="shared" si="6"/>
-        <v>17.12</v>
-      </c>
-      <c r="K23" s="1">
-        <f t="shared" si="7"/>
-        <v>12.839999999999998</v>
-      </c>
-      <c r="L23" s="1">
+        <v>4.9384615384615378</v>
+      </c>
+      <c r="L29" s="1">
+        <f t="shared" si="11"/>
+        <v>3.2923076923076922</v>
+      </c>
+      <c r="M29" s="6">
+        <f t="shared" si="12"/>
+        <v>1.6461538461538461</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="H30" s="11">
+        <f t="shared" si="13"/>
+        <v>11</v>
+      </c>
+      <c r="I30" s="1">
         <f t="shared" si="8"/>
-        <v>8.56</v>
-      </c>
-      <c r="M23" s="6">
+        <v>15.285714285714286</v>
+      </c>
+      <c r="J30" s="1">
         <f t="shared" si="9"/>
-        <v>4.28</v>
-      </c>
-    </row>
-    <row r="24" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H24" s="11">
+        <v>12.22857142857143</v>
+      </c>
+      <c r="K30" s="1">
         <f t="shared" si="10"/>
-        <v>5</v>
-      </c>
-      <c r="I24" s="1">
-        <f>$K$33/I8</f>
-        <v>9.7272727272727266</v>
-      </c>
-      <c r="J24" s="1">
-        <f t="shared" si="6"/>
-        <v>7.7818181818181813</v>
-      </c>
-      <c r="K24" s="1">
-        <f t="shared" si="7"/>
-        <v>5.836363636363636</v>
-      </c>
-      <c r="L24" s="1">
+        <v>9.1714285714285708</v>
+      </c>
+      <c r="L30" s="1">
+        <f t="shared" si="11"/>
+        <v>6.1142857142857148</v>
+      </c>
+      <c r="M30" s="6">
+        <f t="shared" si="12"/>
+        <v>3.0571428571428574</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H31" s="13">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="I31" s="14">
         <f t="shared" si="8"/>
-        <v>3.8909090909090907</v>
-      </c>
-      <c r="M24" s="6">
+        <v>8.2307692307692299</v>
+      </c>
+      <c r="J31" s="14">
         <f t="shared" si="9"/>
-        <v>1.9454545454545453</v>
-      </c>
-    </row>
-    <row r="25" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H25" s="11">
+        <v>6.5846153846153843</v>
+      </c>
+      <c r="K31" s="14">
         <f t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="I25" s="1">
-        <f>$K$33/I9</f>
-        <v>15.285714285714286</v>
-      </c>
-      <c r="J25" s="1">
-        <f t="shared" si="6"/>
-        <v>12.22857142857143</v>
-      </c>
-      <c r="K25" s="1">
-        <f t="shared" si="7"/>
-        <v>9.1714285714285708</v>
-      </c>
-      <c r="L25" s="1">
-        <f t="shared" si="8"/>
-        <v>6.1142857142857148</v>
-      </c>
-      <c r="M25" s="6">
-        <f t="shared" si="9"/>
-        <v>3.0571428571428574</v>
-      </c>
-    </row>
-    <row r="26" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H26" s="11">
-        <f t="shared" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="I26" s="1">
-        <f>$K$33/I10</f>
-        <v>13.375</v>
-      </c>
-      <c r="J26" s="1">
-        <f t="shared" si="6"/>
-        <v>10.700000000000001</v>
-      </c>
-      <c r="K26" s="1">
-        <f t="shared" si="7"/>
-        <v>8.0250000000000004</v>
-      </c>
-      <c r="L26" s="1">
-        <f t="shared" si="8"/>
-        <v>5.3500000000000005</v>
-      </c>
-      <c r="M26" s="6">
-        <f t="shared" si="9"/>
-        <v>2.6750000000000003</v>
-      </c>
-    </row>
-    <row r="27" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H27" s="11">
-        <f t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="I27" s="1">
-        <f>$K$33/I11</f>
-        <v>11.888888888888889</v>
-      </c>
-      <c r="J27" s="1">
-        <f t="shared" si="6"/>
-        <v>9.5111111111111111</v>
-      </c>
-      <c r="K27" s="1">
-        <f t="shared" si="7"/>
-        <v>7.1333333333333337</v>
-      </c>
-      <c r="L27" s="1">
-        <f t="shared" si="8"/>
-        <v>4.7555555555555555</v>
-      </c>
-      <c r="M27" s="6">
-        <f t="shared" si="9"/>
-        <v>2.3777777777777778</v>
-      </c>
-    </row>
-    <row r="28" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H28" s="11">
-        <f t="shared" si="10"/>
-        <v>9</v>
-      </c>
-      <c r="I28" s="1">
-        <f>$K$33/I12</f>
-        <v>17.833333333333332</v>
-      </c>
-      <c r="J28" s="1">
-        <f t="shared" si="6"/>
-        <v>14.266666666666666</v>
-      </c>
-      <c r="K28" s="1">
-        <f t="shared" si="7"/>
-        <v>10.7</v>
-      </c>
-      <c r="L28" s="1">
-        <f t="shared" si="8"/>
-        <v>7.1333333333333329</v>
-      </c>
-      <c r="M28" s="6">
-        <f t="shared" si="9"/>
-        <v>3.5666666666666664</v>
-      </c>
-    </row>
-    <row r="29" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H29" s="11">
-        <f t="shared" si="10"/>
-        <v>10</v>
-      </c>
-      <c r="I29" s="1">
-        <f>$K$33/I13</f>
-        <v>8.2307692307692299</v>
-      </c>
-      <c r="J29" s="1">
-        <f t="shared" si="6"/>
-        <v>6.5846153846153843</v>
-      </c>
-      <c r="K29" s="1">
-        <f t="shared" si="7"/>
         <v>4.9384615384615378</v>
       </c>
-      <c r="L29" s="1">
-        <f t="shared" si="8"/>
+      <c r="L31" s="14">
+        <f t="shared" si="11"/>
         <v>3.2923076923076922</v>
       </c>
-      <c r="M29" s="6">
-        <f t="shared" si="9"/>
+      <c r="M31" s="9">
+        <f t="shared" si="12"/>
         <v>1.6461538461538461</v>
       </c>
     </row>
-    <row r="30" spans="8:13" x14ac:dyDescent="0.25">
-      <c r="H30" s="11">
-        <f t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="I30" s="1">
-        <f>$K$33/I14</f>
-        <v>15.285714285714286</v>
-      </c>
-      <c r="J30" s="1">
-        <f t="shared" si="6"/>
-        <v>12.22857142857143</v>
-      </c>
-      <c r="K30" s="1">
-        <f t="shared" si="7"/>
-        <v>9.1714285714285708</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" si="8"/>
-        <v>6.1142857142857148</v>
-      </c>
-      <c r="M30" s="6">
-        <f t="shared" si="9"/>
-        <v>3.0571428571428574</v>
-      </c>
-    </row>
-    <row r="31" spans="8:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H31" s="13">
-        <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="I31" s="14">
-        <f>$K$33/I15</f>
-        <v>8.2307692307692299</v>
-      </c>
-      <c r="J31" s="14">
-        <f t="shared" si="6"/>
-        <v>6.5846153846153843</v>
-      </c>
-      <c r="K31" s="14">
-        <f t="shared" si="7"/>
-        <v>4.9384615384615378</v>
-      </c>
-      <c r="L31" s="14">
-        <f t="shared" si="8"/>
-        <v>3.2923076923076922</v>
-      </c>
-      <c r="M31" s="9">
-        <f t="shared" si="9"/>
-        <v>1.6461538461538461</v>
-      </c>
-    </row>
-    <row r="32" spans="8:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:13" x14ac:dyDescent="0.3">
       <c r="H32"/>
     </row>
-    <row r="33" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="8:16" x14ac:dyDescent="0.3">
       <c r="H33"/>
       <c r="J33" t="s">
         <v>16</v>
@@ -1427,14 +1642,21 @@
       <c r="K33">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="O33" t="s">
+        <v>17</v>
+      </c>
+      <c r="P33">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="8:16" x14ac:dyDescent="0.3">
       <c r="H34"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="H2:M2"/>
     <mergeCell ref="H18:M18"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
